--- a/Grids Germany/No leap years/Saxony insights/[Saxony][Euclidean][Raw]Yearly_normality.xlsx
+++ b/Grids Germany/No leap years/Saxony insights/[Saxony][Euclidean][Raw]Yearly_normality.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,52 +429,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>YEAR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n_P1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>n_P2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P1_W</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P1_p</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>P1_Normality</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P2_W</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P2_p</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>P2_Normality</t>
         </is>
@@ -478,16 +490,16 @@
         <v>1996</v>
       </c>
       <c r="C2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D2" t="n">
         <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9705767631530762</v>
+        <v>0.9748921990394592</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2786228358745575</v>
+        <v>0.4153035283088684</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -495,10 +507,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.7968633770942688</v>
+        <v>0.7971847057342529</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004565615206956863</v>
+        <v>0.004607341717928648</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -516,16 +528,16 @@
         <v>1997</v>
       </c>
       <c r="C3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3" t="n">
         <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9573840498924255</v>
+        <v>0.9592302441596985</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08471003919839859</v>
+        <v>0.1069986522197723</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -533,10 +545,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.9457123279571533</v>
+        <v>0.9443546533584595</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4963231086730957</v>
+        <v>0.4769353568553925</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -554,16 +566,16 @@
         <v>1998</v>
       </c>
       <c r="C4" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D4" t="n">
         <v>14</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9745627045631409</v>
+        <v>0.9757850170135498</v>
       </c>
       <c r="F4" t="n">
-        <v>0.390649139881134</v>
+        <v>0.4454798996448517</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -571,10 +583,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.8170945048332214</v>
+        <v>0.842242419719696</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008184893988072872</v>
+        <v>0.01745624653995037</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -592,16 +604,16 @@
         <v>1999</v>
       </c>
       <c r="C5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5" t="n">
         <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9714633822441101</v>
+        <v>0.9649912118911743</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3008616864681244</v>
+        <v>0.1789533793926239</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -609,10 +621,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.9074445962905884</v>
+        <v>0.9545620679855347</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1446747332811356</v>
+        <v>0.6334920525550842</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -630,16 +642,16 @@
         <v>2000</v>
       </c>
       <c r="C6" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D6" t="n">
         <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>0.937046229839325</v>
+        <v>0.9485743641853333</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01379304565489292</v>
+        <v>0.04133506864309311</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -647,10 +659,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.8634923696517944</v>
+        <v>0.8643071055412292</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03403521701693535</v>
+        <v>0.0349348746240139</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -668,16 +680,16 @@
         <v>2001</v>
       </c>
       <c r="C7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D7" t="n">
         <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9773374199867249</v>
+        <v>0.9660108089447021</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4871542155742645</v>
+        <v>0.1958216726779938</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -685,10 +697,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.8076400756835938</v>
+        <v>0.862985372543335</v>
       </c>
       <c r="I7" t="n">
-        <v>0.006213414948433638</v>
+        <v>0.03348777070641518</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -706,16 +718,16 @@
         <v>2002</v>
       </c>
       <c r="C8" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" t="n">
         <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9812041521072388</v>
+        <v>0.9757161736488342</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6425602436065674</v>
+        <v>0.4431009888648987</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -723,10 +735,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.9519161581993103</v>
+        <v>0.9331111311912537</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5908325910568237</v>
+        <v>0.3371846675872803</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -744,16 +756,16 @@
         <v>2003</v>
       </c>
       <c r="C9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D9" t="n">
         <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9350237250328064</v>
+        <v>0.9284359216690063</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01159424055367708</v>
+        <v>0.007411598693579435</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -761,10 +773,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.8811711072921753</v>
+        <v>0.8802237510681152</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06039261445403099</v>
+        <v>0.05854341015219688</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -782,16 +794,16 @@
         <v>2004</v>
       </c>
       <c r="C10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D10" t="n">
         <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9825798869132996</v>
+        <v>0.9833929538726807</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7008402347564697</v>
+        <v>0.7464178800582886</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -799,10 +811,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.8498544096946716</v>
+        <v>0.8554379940032959</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02210939861834049</v>
+        <v>0.02634806744754314</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -820,16 +832,16 @@
         <v>2005</v>
       </c>
       <c r="C11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D11" t="n">
         <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9743321537971497</v>
+        <v>0.9777108430862427</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3833100199699402</v>
+        <v>0.5154664516448975</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -837,10 +849,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.8456223607063293</v>
+        <v>0.8620322942733765</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01937962137162685</v>
+        <v>0.0324835292994976</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -858,16 +870,16 @@
         <v>2006</v>
       </c>
       <c r="C12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D12" t="n">
         <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>0.933470606803894</v>
+        <v>0.9307737946510315</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0101567767560482</v>
+        <v>0.008986226283013821</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -875,10 +887,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.9736557602882385</v>
+        <v>0.9906195402145386</v>
       </c>
       <c r="I12" t="n">
-        <v>0.921357274055481</v>
+        <v>0.9997168183326721</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -896,16 +908,16 @@
         <v>2007</v>
       </c>
       <c r="C13" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D13" t="n">
         <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9790801405906677</v>
+        <v>0.9779993891716003</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5548061728477478</v>
+        <v>0.5264811515808105</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -913,10 +925,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.9777993559837341</v>
+        <v>0.9742420315742493</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9600412845611572</v>
+        <v>0.9276577830314636</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -934,27 +946,27 @@
         <v>2008</v>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
         <v>14</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9566702246665955</v>
+        <v>0.9458014369010925</v>
       </c>
       <c r="F14" t="n">
-        <v>0.07936318218708038</v>
+        <v>0.03238453343510628</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.9551247954368591</v>
+        <v>0.9733191728591919</v>
       </c>
       <c r="I14" t="n">
-        <v>0.642686665058136</v>
+        <v>0.9176238179206848</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -972,16 +984,16 @@
         <v>2009</v>
       </c>
       <c r="C15" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D15" t="n">
         <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9816213250160217</v>
+        <v>0.9836952686309814</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6601955890655518</v>
+        <v>0.7587382197380066</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -989,10 +1001,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.9499152898788452</v>
+        <v>0.9155610203742981</v>
       </c>
       <c r="I15" t="n">
-        <v>0.559390664100647</v>
+        <v>0.1897377073764801</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1010,16 +1022,16 @@
         <v>2010</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
         <v>14</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9698221683502197</v>
+        <v>0.9718426465988159</v>
       </c>
       <c r="F16" t="n">
-        <v>0.260843813419342</v>
+        <v>0.3237696290016174</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1027,10 +1039,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.9131847023963928</v>
+        <v>0.9211171269416809</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1752801090478897</v>
+        <v>0.2281775325536728</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1048,16 +1060,16 @@
         <v>2011</v>
       </c>
       <c r="C17" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D17" t="n">
         <v>14</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9645547866821289</v>
+        <v>0.9617456793785095</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1629046499729156</v>
+        <v>0.1340379863977432</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1065,10 +1077,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.8971114158630371</v>
+        <v>0.8953847885131836</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1024138107895851</v>
+        <v>0.09668383747339249</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1086,16 +1098,16 @@
         <v>2012</v>
       </c>
       <c r="C18" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9326366782188416</v>
+        <v>0.9263571500778198</v>
       </c>
       <c r="F18" t="n">
-        <v>0.009463254362344742</v>
+        <v>0.006254793610423803</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1103,10 +1115,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.9514952301979065</v>
+        <v>0.9558160305023193</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5841532349586487</v>
+        <v>0.6540251970291138</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1124,27 +1136,27 @@
         <v>2013</v>
       </c>
       <c r="C19" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D19" t="n">
         <v>14</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9417404532432556</v>
+        <v>0.9522619247436523</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02075176127254963</v>
+        <v>0.05734043940901756</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.9481481313705444</v>
+        <v>0.9361564517021179</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5323423743247986</v>
+        <v>0.3712962567806244</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1162,16 +1174,16 @@
         <v>2014</v>
       </c>
       <c r="C20" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D20" t="n">
         <v>14</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9562846422195435</v>
+        <v>0.9660987257957458</v>
       </c>
       <c r="F20" t="n">
-        <v>0.07661833614110947</v>
+        <v>0.1973446160554886</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1179,10 +1191,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.9437726736068726</v>
+        <v>0.9437321424484253</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4687820374965668</v>
+        <v>0.4682177305221558</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1200,16 +1212,16 @@
         <v>2015</v>
       </c>
       <c r="C21" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D21" t="n">
         <v>14</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9846037626266479</v>
+        <v>0.983014702796936</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7850135564804077</v>
+        <v>0.7308778762817383</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1217,10 +1229,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.9490941166877747</v>
+        <v>0.9386767148971558</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5467314720153809</v>
+        <v>0.401629775762558</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1238,16 +1250,16 @@
         <v>2016</v>
       </c>
       <c r="C22" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D22" t="n">
         <v>14</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9580333828926086</v>
+        <v>0.9683352708816528</v>
       </c>
       <c r="F22" t="n">
-        <v>0.08988808840513229</v>
+        <v>0.2399980872869492</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1255,10 +1267,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.9117972850799561</v>
+        <v>0.9532185792922974</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1673433184623718</v>
+        <v>0.6116991639137268</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1276,16 +1288,16 @@
         <v>2017</v>
       </c>
       <c r="C23" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D23" t="n">
         <v>14</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9657843112945557</v>
+        <v>0.9681609869003296</v>
       </c>
       <c r="F23" t="n">
-        <v>0.182051807641983</v>
+        <v>0.2363922595977783</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1293,10 +1305,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.9388459324836731</v>
+        <v>0.9205549955368042</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4037349820137024</v>
+        <v>0.2239735126495361</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1314,27 +1326,27 @@
         <v>2018</v>
       </c>
       <c r="C24" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D24" t="n">
         <v>14</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9004641771316528</v>
+        <v>0.9577166438102722</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0007451943820342422</v>
+        <v>0.09341640770435333</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.8390282988548279</v>
+        <v>0.8492400050163269</v>
       </c>
       <c r="I24" t="n">
-        <v>0.01581405662000179</v>
+        <v>0.02168906107544899</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1352,16 +1364,16 @@
         <v>2019</v>
       </c>
       <c r="C25" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D25" t="n">
         <v>14</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9784214496612549</v>
+        <v>0.9779683351516724</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5286767482757568</v>
+        <v>0.5252889394760132</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1369,10 +1381,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.7851132154464722</v>
+        <v>0.7571896314620972</v>
       </c>
       <c r="I25" t="n">
-        <v>0.003285800339654088</v>
+        <v>0.001546580693684518</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1390,16 +1402,16 @@
         <v>2020</v>
       </c>
       <c r="C26" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D26" t="n">
         <v>14</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9776719808578491</v>
+        <v>0.981846034526825</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4997586905956268</v>
+        <v>0.682343602180481</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1407,10 +1419,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.970366895198822</v>
+        <v>0.9613857865333557</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8815265893936157</v>
+        <v>0.7458469271659851</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1428,16 +1440,16 @@
         <v>2021</v>
       </c>
       <c r="C27" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D27" t="n">
         <v>14</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9532158970832825</v>
+        <v>0.9585297107696533</v>
       </c>
       <c r="F27" t="n">
-        <v>0.05793473869562149</v>
+        <v>0.1004830971360207</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1445,10 +1457,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.9334220886230469</v>
+        <v>0.9224855303764343</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3405416309833527</v>
+        <v>0.2387246042490005</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1466,16 +1478,16 @@
         <v>2022</v>
       </c>
       <c r="C28" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D28" t="n">
         <v>14</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9873263835906982</v>
+        <v>0.9896618723869324</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8854605555534363</v>
+        <v>0.95245361328125</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1483,10 +1495,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.8976688981056213</v>
+        <v>0.917418360710144</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1043368577957153</v>
+        <v>0.201837494969368</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1504,16 +1516,16 @@
         <v>2023</v>
       </c>
       <c r="C29" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D29" t="n">
         <v>14</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9835776090621948</v>
+        <v>0.9855803251266479</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7428444623947144</v>
+        <v>0.832219660282135</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1521,10 +1533,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.9350055456161499</v>
+        <v>0.9309116005897522</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3580797016620636</v>
+        <v>0.3142443597316742</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1542,16 +1554,16 @@
         <v>2024</v>
       </c>
       <c r="C30" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D30" t="n">
         <v>14</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9140262603759766</v>
+        <v>0.8848546743392944</v>
       </c>
       <c r="F30" t="n">
-        <v>0.00208299676887691</v>
+        <v>0.0002845205017365515</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1559,10 +1571,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.8269514441490173</v>
+        <v>0.8228322267532349</v>
       </c>
       <c r="I30" t="n">
-        <v>0.01096715684980154</v>
+        <v>0.009698373265564442</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1580,16 +1592,16 @@
         <v>2025</v>
       </c>
       <c r="C31" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D31" t="n">
         <v>14</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9803466200828552</v>
+        <v>0.9670846462249756</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6066165566444397</v>
+        <v>0.2151984572410583</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1597,10 +1609,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.8546768426895142</v>
+        <v>0.8424220085144043</v>
       </c>
       <c r="I31" t="n">
-        <v>0.02572299353778362</v>
+        <v>0.01755316369235516</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1618,16 +1630,16 @@
         <v>1996</v>
       </c>
       <c r="C32" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D32" t="n">
         <v>14</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9126223921775818</v>
+        <v>0.9120814800262451</v>
       </c>
       <c r="F32" t="n">
-        <v>0.001867434126324952</v>
+        <v>0.002030142350122333</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1635,10 +1647,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.8841097354888916</v>
+        <v>0.9103507995605469</v>
       </c>
       <c r="I32" t="n">
-        <v>0.06652431935071945</v>
+        <v>0.1594453006982803</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1656,16 +1668,16 @@
         <v>1997</v>
       </c>
       <c r="C33" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D33" t="n">
         <v>14</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9846559166908264</v>
+        <v>0.9880849719047546</v>
       </c>
       <c r="F33" t="n">
-        <v>0.787114143371582</v>
+        <v>0.9143224954605103</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1673,10 +1685,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.9221411347389221</v>
+        <v>0.9267752766609192</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2360277026891708</v>
+        <v>0.2748101949691772</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1694,16 +1706,16 @@
         <v>1998</v>
       </c>
       <c r="C34" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D34" t="n">
         <v>14</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9786680936813354</v>
+        <v>0.9703729748725891</v>
       </c>
       <c r="F34" t="n">
-        <v>0.53838711977005</v>
+        <v>0.2859850227832794</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1711,10 +1723,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.9126901626586914</v>
+        <v>0.9109002947807312</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1724099218845367</v>
+        <v>0.1624013483524323</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1732,16 +1744,16 @@
         <v>1999</v>
       </c>
       <c r="C35" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D35" t="n">
         <v>14</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9823552966117859</v>
+        <v>0.979400634765625</v>
       </c>
       <c r="F35" t="n">
-        <v>0.691320538520813</v>
+        <v>0.5816375017166138</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1749,10 +1761,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.9505356550216675</v>
+        <v>0.958227276802063</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5690522193908691</v>
+        <v>0.6938149333000183</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1770,16 +1782,16 @@
         <v>2000</v>
       </c>
       <c r="C36" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D36" t="n">
         <v>14</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9529975652694702</v>
+        <v>0.9648963809013367</v>
       </c>
       <c r="F36" t="n">
-        <v>0.05679715424776077</v>
+        <v>0.1774563938379288</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1787,10 +1799,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.9234288930892944</v>
+        <v>0.9236866235733032</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2462609112262726</v>
+        <v>0.2483578771352768</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1808,16 +1820,16 @@
         <v>2001</v>
       </c>
       <c r="C37" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D37" t="n">
         <v>14</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9813925623893738</v>
+        <v>0.9775872826576233</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6505160331726074</v>
+        <v>0.5107873678207397</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1825,10 +1837,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.9203794002532959</v>
+        <v>0.9223485589027405</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2226756066083908</v>
+        <v>0.2376485466957092</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -1846,16 +1858,16 @@
         <v>2002</v>
       </c>
       <c r="C38" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D38" t="n">
         <v>14</v>
       </c>
       <c r="E38" t="n">
-        <v>0.963315486907959</v>
+        <v>0.9669138789176941</v>
       </c>
       <c r="F38" t="n">
-        <v>0.145572304725647</v>
+        <v>0.2120024859905243</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1863,10 +1875,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.9300944209098816</v>
+        <v>0.945065438747406</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3060756921768188</v>
+        <v>0.4870217740535736</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -1884,16 +1896,16 @@
         <v>2003</v>
       </c>
       <c r="C39" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D39" t="n">
         <v>14</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9605842232704163</v>
+        <v>0.967574417591095</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1134848296642303</v>
+        <v>0.2246156334877014</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1901,10 +1913,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.916703462600708</v>
+        <v>0.932520866394043</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1970946043729782</v>
+        <v>0.3308901488780975</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -1922,16 +1934,16 @@
         <v>2004</v>
       </c>
       <c r="C40" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D40" t="n">
         <v>14</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9690057635307312</v>
+        <v>0.9635810256004333</v>
       </c>
       <c r="F40" t="n">
-        <v>0.242756649851799</v>
+        <v>0.1578900516033173</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1939,14 +1951,14 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.8611704111099243</v>
+        <v>0.9019957780838013</v>
       </c>
       <c r="I40" t="n">
-        <v>0.03160254657268524</v>
+        <v>0.1205652132630348</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1960,16 +1972,16 @@
         <v>2005</v>
       </c>
       <c r="C41" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D41" t="n">
         <v>14</v>
       </c>
       <c r="E41" t="n">
-        <v>0.967913031578064</v>
+        <v>0.9809291958808899</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2203281223773956</v>
+        <v>0.6441991925239563</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1977,10 +1989,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.903017520904541</v>
+        <v>0.9033175706863403</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1247564107179642</v>
+        <v>0.1260150223970413</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -1998,16 +2010,16 @@
         <v>2006</v>
       </c>
       <c r="C42" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D42" t="n">
         <v>14</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9627568125724792</v>
+        <v>0.968635618686676</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1383574903011322</v>
+        <v>0.2463296800851822</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2015,10 +2027,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.9615257382392883</v>
+        <v>0.9600948691368103</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7481333017349243</v>
+        <v>0.7246589660644531</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2036,16 +2048,16 @@
         <v>2007</v>
       </c>
       <c r="C43" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D43" t="n">
         <v>14</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9447607398033142</v>
+        <v>0.9466620683670044</v>
       </c>
       <c r="F43" t="n">
-        <v>0.02709286287426949</v>
+        <v>0.03492520749568939</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2053,10 +2065,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.9474425315856934</v>
+        <v>0.9781894087791443</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5217514634132385</v>
+        <v>0.9629553556442261</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2074,16 +2086,16 @@
         <v>2008</v>
       </c>
       <c r="C44" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D44" t="n">
         <v>14</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9734644293785095</v>
+        <v>0.9775843024253845</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3566435873508453</v>
+        <v>0.5106756091117859</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2091,14 +2103,14 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.9134268164634705</v>
+        <v>0.8569748401641846</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1767026335000992</v>
+        <v>0.02765955962240696</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -2112,16 +2124,16 @@
         <v>2009</v>
       </c>
       <c r="C45" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D45" t="n">
         <v>14</v>
       </c>
       <c r="E45" t="n">
-        <v>0.972137987613678</v>
+        <v>0.9758901000022888</v>
       </c>
       <c r="F45" t="n">
-        <v>0.31878861784935</v>
+        <v>0.4491299986839294</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2129,10 +2141,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.9361674189567566</v>
+        <v>0.9456300139427185</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3714240193367004</v>
+        <v>0.4951331615447998</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2150,16 +2162,16 @@
         <v>2010</v>
       </c>
       <c r="C46" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D46" t="n">
         <v>14</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9584295749664307</v>
+        <v>0.965056300163269</v>
       </c>
       <c r="F46" t="n">
-        <v>0.09320203959941864</v>
+        <v>0.1799871474504471</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2167,10 +2179,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.8848404288291931</v>
+        <v>0.883399486541748</v>
       </c>
       <c r="I46" t="n">
-        <v>0.06814682483673096</v>
+        <v>0.06498535722494125</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2188,16 +2200,16 @@
         <v>2011</v>
       </c>
       <c r="C47" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D47" t="n">
         <v>14</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9699487686157227</v>
+        <v>0.9618626236915588</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2637549638748169</v>
+        <v>0.1354467570781708</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2205,10 +2217,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.9223861694335938</v>
+        <v>0.9391255974769592</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2379434257745743</v>
+        <v>0.4072336256504059</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2226,16 +2238,16 @@
         <v>2012</v>
       </c>
       <c r="C48" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D48" t="n">
         <v>14</v>
       </c>
       <c r="E48" t="n">
-        <v>0.982513427734375</v>
+        <v>0.9751018881797791</v>
       </c>
       <c r="F48" t="n">
-        <v>0.6980234384536743</v>
+        <v>0.4222553372383118</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2243,10 +2255,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.9365453720092773</v>
+        <v>0.954596996307373</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3758521676063538</v>
+        <v>0.6340616345405579</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2264,16 +2276,16 @@
         <v>2013</v>
       </c>
       <c r="C49" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D49" t="n">
         <v>14</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9816396832466125</v>
+        <v>0.9833663105964661</v>
       </c>
       <c r="F49" t="n">
-        <v>0.6609746813774109</v>
+        <v>0.7453280091285706</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2281,10 +2293,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.9406946301460266</v>
+        <v>0.9292528033256531</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4272977113723755</v>
+        <v>0.2978600263595581</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2302,16 +2314,16 @@
         <v>2014</v>
       </c>
       <c r="C50" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D50" t="n">
         <v>14</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9825989007949829</v>
+        <v>0.9803303480148315</v>
       </c>
       <c r="F50" t="n">
-        <v>0.7016447186470032</v>
+        <v>0.6194696426391602</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2319,10 +2331,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.9744917154312134</v>
+        <v>0.9734063148498535</v>
       </c>
       <c r="I50" t="n">
-        <v>0.9302619099617004</v>
+        <v>0.9185986518859863</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2340,16 +2352,16 @@
         <v>2015</v>
       </c>
       <c r="C51" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D51" t="n">
         <v>14</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9791147708892822</v>
+        <v>0.9789673686027527</v>
       </c>
       <c r="F51" t="n">
-        <v>0.5561975836753845</v>
+        <v>0.5643128156661987</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2357,10 +2369,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.940329909324646</v>
+        <v>0.9286050200462341</v>
       </c>
       <c r="I51" t="n">
-        <v>0.4225679636001587</v>
+        <v>0.2916710078716278</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2378,16 +2390,16 @@
         <v>2016</v>
       </c>
       <c r="C52" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D52" t="n">
         <v>14</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9731581211090088</v>
+        <v>0.976830780506134</v>
       </c>
       <c r="F52" t="n">
-        <v>0.3475924134254456</v>
+        <v>0.4826914370059967</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2395,10 +2407,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.8771160840988159</v>
+        <v>0.9396542906761169</v>
       </c>
       <c r="I52" t="n">
-        <v>0.05288008600473404</v>
+        <v>0.4139121472835541</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2416,16 +2428,16 @@
         <v>2017</v>
       </c>
       <c r="C53" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D53" t="n">
         <v>14</v>
       </c>
       <c r="E53" t="n">
-        <v>0.9635288119316101</v>
+        <v>0.9652990102767944</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1484232246875763</v>
+        <v>0.1838952004909515</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2433,10 +2445,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.8983739018440247</v>
+        <v>0.9125340580940247</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1068216264247894</v>
+        <v>0.1715133786201477</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2454,27 +2466,27 @@
         <v>2018</v>
       </c>
       <c r="C54" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D54" t="n">
         <v>14</v>
       </c>
       <c r="E54" t="n">
-        <v>0.9719269871711731</v>
+        <v>0.9472751617431641</v>
       </c>
       <c r="F54" t="n">
-        <v>0.3130865395069122</v>
+        <v>0.03686011582612991</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.8923091888427734</v>
+        <v>0.9048497080802917</v>
       </c>
       <c r="I54" t="n">
-        <v>0.08727547526359558</v>
+        <v>0.1326427906751633</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2492,16 +2504,16 @@
         <v>2019</v>
       </c>
       <c r="C55" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D55" t="n">
         <v>14</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9654408693313599</v>
+        <v>0.960542619228363</v>
       </c>
       <c r="F55" t="n">
-        <v>0.176497146487236</v>
+        <v>0.1203551068902016</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2509,10 +2521,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.9678765535354614</v>
+        <v>0.9752023816108704</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8470331430435181</v>
+        <v>0.9374077916145325</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2530,16 +2542,16 @@
         <v>2020</v>
       </c>
       <c r="C56" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D56" t="n">
         <v>14</v>
       </c>
       <c r="E56" t="n">
-        <v>0.9529628753662109</v>
+        <v>0.9711925387382507</v>
       </c>
       <c r="F56" t="n">
-        <v>0.05661847069859505</v>
+        <v>0.3065605163574219</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2547,10 +2559,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.9337339997291565</v>
+        <v>0.9506996273994446</v>
       </c>
       <c r="I56" t="n">
-        <v>0.3439378440380096</v>
+        <v>0.5716192722320557</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2568,16 +2580,16 @@
         <v>2021</v>
       </c>
       <c r="C57" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D57" t="n">
         <v>14</v>
       </c>
       <c r="E57" t="n">
-        <v>0.9857513904571533</v>
+        <v>0.9852432012557983</v>
       </c>
       <c r="F57" t="n">
-        <v>0.8299171328544617</v>
+        <v>0.819624662399292</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2585,10 +2597,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0.9726973176002502</v>
+        <v>0.9735705852508545</v>
       </c>
       <c r="I57" t="n">
-        <v>0.910510778427124</v>
+        <v>0.9204205274581909</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2606,16 +2618,16 @@
         <v>2022</v>
       </c>
       <c r="C58" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D58" t="n">
         <v>14</v>
       </c>
       <c r="E58" t="n">
-        <v>0.9416042566299438</v>
+        <v>0.9360460042953491</v>
       </c>
       <c r="F58" t="n">
-        <v>0.02050511725246906</v>
+        <v>0.01397169195115566</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2623,10 +2635,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0.9755489230155945</v>
+        <v>0.9696952104568481</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9407470226287842</v>
+        <v>0.8725495338439941</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -2644,27 +2656,27 @@
         <v>2023</v>
       </c>
       <c r="C59" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D59" t="n">
         <v>14</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9508190751075745</v>
+        <v>0.9516919851303101</v>
       </c>
       <c r="F59" t="n">
-        <v>0.04662369191646576</v>
+        <v>0.05450234934687614</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0.9239050149917603</v>
+        <v>0.9170743227005005</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2501476109027863</v>
+        <v>0.1995416730642319</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -2682,16 +2694,16 @@
         <v>2024</v>
       </c>
       <c r="C60" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D60" t="n">
         <v>14</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9734081625938416</v>
+        <v>0.9720249176025391</v>
       </c>
       <c r="F60" t="n">
-        <v>0.3549664914608002</v>
+        <v>0.3287383317947388</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2699,10 +2711,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0.9545741081237793</v>
+        <v>0.9567033052444458</v>
       </c>
       <c r="I60" t="n">
-        <v>0.6336879730224609</v>
+        <v>0.6686345934867859</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2720,27 +2732,27 @@
         <v>2025</v>
       </c>
       <c r="C61" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D61" t="n">
         <v>14</v>
       </c>
       <c r="E61" t="n">
-        <v>0.953389585018158</v>
+        <v>0.9444211721420288</v>
       </c>
       <c r="F61" t="n">
-        <v>0.05885635316371918</v>
+        <v>0.02870249934494495</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.9717237949371338</v>
+        <v>0.9698457717895508</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8988333940505981</v>
+        <v>0.8745848536491394</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -2758,16 +2770,16 @@
         <v>1996</v>
       </c>
       <c r="C62" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D62" t="n">
         <v>14</v>
       </c>
       <c r="E62" t="n">
-        <v>0.9272156357765198</v>
+        <v>0.9181111454963684</v>
       </c>
       <c r="F62" t="n">
-        <v>0.006011997815221548</v>
+        <v>0.00323785562068224</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2775,10 +2787,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0.966015100479126</v>
+        <v>0.9771026372909546</v>
       </c>
       <c r="I62" t="n">
-        <v>0.81935054063797</v>
+        <v>0.9545174837112427</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -2796,16 +2808,16 @@
         <v>1997</v>
       </c>
       <c r="C63" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D63" t="n">
         <v>14</v>
       </c>
       <c r="E63" t="n">
-        <v>0.9660380482673645</v>
+        <v>0.9740191698074341</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1862612217664719</v>
+        <v>0.3872634172439575</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2813,10 +2825,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0.8973328471183777</v>
+        <v>0.8924157023429871</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1031732484698296</v>
+        <v>0.08758512139320374</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -2834,16 +2846,16 @@
         <v>1998</v>
       </c>
       <c r="C64" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D64" t="n">
         <v>14</v>
       </c>
       <c r="E64" t="n">
-        <v>0.9609876275062561</v>
+        <v>0.9681318998336792</v>
       </c>
       <c r="F64" t="n">
-        <v>0.117743656039238</v>
+        <v>0.2357952445745468</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2851,10 +2863,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0.9516510963439941</v>
+        <v>0.9427893757820129</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5866228938102722</v>
+        <v>0.4552284479141235</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -2872,16 +2884,16 @@
         <v>1999</v>
       </c>
       <c r="C65" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D65" t="n">
         <v>14</v>
       </c>
       <c r="E65" t="n">
-        <v>0.9690116047859192</v>
+        <v>0.9657378196716309</v>
       </c>
       <c r="F65" t="n">
-        <v>0.242882177233696</v>
+        <v>0.1911643445491791</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2889,10 +2901,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0.9843286871910095</v>
+        <v>0.9796515703201294</v>
       </c>
       <c r="I65" t="n">
-        <v>0.9925920367240906</v>
+        <v>0.972739577293396</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -2910,16 +2922,16 @@
         <v>2000</v>
       </c>
       <c r="C66" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D66" t="n">
         <v>14</v>
       </c>
       <c r="E66" t="n">
-        <v>0.9517390727996826</v>
+        <v>0.9601227641105652</v>
       </c>
       <c r="F66" t="n">
-        <v>0.05067063495516777</v>
+        <v>0.1159113273024559</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2927,10 +2939,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0.9849251508712769</v>
+        <v>0.9706863760948181</v>
       </c>
       <c r="I66" t="n">
-        <v>0.9940185546875</v>
+        <v>0.8857038021087646</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -2948,16 +2960,16 @@
         <v>2001</v>
       </c>
       <c r="C67" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D67" t="n">
         <v>14</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9181037545204163</v>
+        <v>0.9316990375518799</v>
       </c>
       <c r="F67" t="n">
-        <v>0.002871825359761715</v>
+        <v>0.009703224524855614</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2965,10 +2977,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0.969731330871582</v>
+        <v>0.9863933324813843</v>
       </c>
       <c r="I67" t="n">
-        <v>0.873039186000824</v>
+        <v>0.9966859221458435</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -2986,16 +2998,16 @@
         <v>2002</v>
       </c>
       <c r="C68" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D68" t="n">
         <v>14</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9591588377952576</v>
+        <v>0.9665794968605042</v>
       </c>
       <c r="F68" t="n">
-        <v>0.09962604194879532</v>
+        <v>0.2058712691068649</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3003,10 +3015,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0.9554333090782166</v>
+        <v>0.951433002948761</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6477416753768921</v>
+        <v>0.5831680297851562</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3024,16 +3036,16 @@
         <v>2003</v>
       </c>
       <c r="C69" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D69" t="n">
         <v>14</v>
       </c>
       <c r="E69" t="n">
-        <v>0.9773658514022827</v>
+        <v>0.9841662645339966</v>
       </c>
       <c r="F69" t="n">
-        <v>0.4882180094718933</v>
+        <v>0.7777003049850464</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3041,10 +3053,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0.9454833269119263</v>
+        <v>0.9342559576034546</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4930164813995361</v>
+        <v>0.3496844172477722</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3062,16 +3074,16 @@
         <v>2004</v>
       </c>
       <c r="C70" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D70" t="n">
         <v>14</v>
       </c>
       <c r="E70" t="n">
-        <v>0.9656515717506409</v>
+        <v>0.9615616202354431</v>
       </c>
       <c r="F70" t="n">
-        <v>0.1798857152462006</v>
+        <v>0.1318498998880386</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3079,10 +3091,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0.7792688608169556</v>
+        <v>0.7860773205757141</v>
       </c>
       <c r="I70" t="n">
-        <v>0.002797339810058475</v>
+        <v>0.003374776570126414</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3100,16 +3112,16 @@
         <v>2005</v>
       </c>
       <c r="C71" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D71" t="n">
         <v>14</v>
       </c>
       <c r="E71" t="n">
-        <v>0.9431789517402649</v>
+        <v>0.9276280999183655</v>
       </c>
       <c r="F71" t="n">
-        <v>0.02355329506099224</v>
+        <v>0.006937372032552958</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3117,10 +3129,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0.9086250066757202</v>
+        <v>0.9082545042037964</v>
       </c>
       <c r="I71" t="n">
-        <v>0.1505026817321777</v>
+        <v>0.1486490219831467</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3138,16 +3150,16 @@
         <v>2006</v>
       </c>
       <c r="C72" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D72" t="n">
         <v>14</v>
       </c>
       <c r="E72" t="n">
-        <v>0.9330734610557556</v>
+        <v>0.9434030055999756</v>
       </c>
       <c r="F72" t="n">
-        <v>0.009820064529776573</v>
+        <v>0.02626655250787735</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3155,10 +3167,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0.8466727733612061</v>
+        <v>0.6232798099517822</v>
       </c>
       <c r="I72" t="n">
-        <v>0.0200220849364996</v>
+        <v>6.591119017684832e-05</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3176,16 +3188,16 @@
         <v>2007</v>
       </c>
       <c r="C73" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D73" t="n">
         <v>14</v>
       </c>
       <c r="E73" t="n">
-        <v>0.9409517049789429</v>
+        <v>0.9301177859306335</v>
       </c>
       <c r="F73" t="n">
-        <v>0.01936528459191322</v>
+        <v>0.008511718362569809</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3193,10 +3205,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0.9379987120628357</v>
+        <v>0.942346453666687</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3932813704013824</v>
+        <v>0.4492148458957672</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3214,16 +3226,16 @@
         <v>2008</v>
       </c>
       <c r="C74" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D74" t="n">
         <v>14</v>
       </c>
       <c r="E74" t="n">
-        <v>0.9433836340904236</v>
+        <v>0.929486870765686</v>
       </c>
       <c r="F74" t="n">
-        <v>0.02398284897208214</v>
+        <v>0.008080190047621727</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3231,10 +3243,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>0.9056258201599121</v>
+        <v>0.894731342792511</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1361328214406967</v>
+        <v>0.09460162371397018</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3252,16 +3264,16 @@
         <v>2009</v>
       </c>
       <c r="C75" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D75" t="n">
         <v>14</v>
       </c>
       <c r="E75" t="n">
-        <v>0.9729649424552917</v>
+        <v>0.9744601845741272</v>
       </c>
       <c r="F75" t="n">
-        <v>0.3419787585735321</v>
+        <v>0.4012445211410522</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3269,10 +3281,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0.8109763860702515</v>
+        <v>0.8252615928649902</v>
       </c>
       <c r="I75" t="n">
-        <v>0.006844162009656429</v>
+        <v>0.01042651012539864</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3290,16 +3302,16 @@
         <v>2010</v>
       </c>
       <c r="C76" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D76" t="n">
         <v>14</v>
       </c>
       <c r="E76" t="n">
-        <v>0.9567286968231201</v>
+        <v>0.9544032216072083</v>
       </c>
       <c r="F76" t="n">
-        <v>0.0797882080078125</v>
+        <v>0.06942238658666611</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3307,10 +3319,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0.9387560486793518</v>
+        <v>0.9403423070907593</v>
       </c>
       <c r="I76" t="n">
-        <v>0.4026159942150116</v>
+        <v>0.4227281808853149</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3328,16 +3340,16 @@
         <v>2011</v>
       </c>
       <c r="C77" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D77" t="n">
         <v>14</v>
       </c>
       <c r="E77" t="n">
-        <v>0.9561193585395813</v>
+        <v>0.9618368148803711</v>
       </c>
       <c r="F77" t="n">
-        <v>0.07547125965356827</v>
+        <v>0.1351350843906403</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3345,10 +3357,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0.9655757546424866</v>
+        <v>0.9757010340690613</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8126233816146851</v>
+        <v>0.9421827793121338</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3366,16 +3378,16 @@
         <v>2012</v>
       </c>
       <c r="C78" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D78" t="n">
         <v>14</v>
       </c>
       <c r="E78" t="n">
-        <v>0.9521794319152832</v>
+        <v>0.9530050754547119</v>
       </c>
       <c r="F78" t="n">
-        <v>0.05273338407278061</v>
+        <v>0.06126987934112549</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3383,10 +3395,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>0.9844567179679871</v>
+        <v>0.9796456694602966</v>
       </c>
       <c r="I78" t="n">
-        <v>0.9929164052009583</v>
+        <v>0.9727035760879517</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3404,27 +3416,27 @@
         <v>2013</v>
       </c>
       <c r="C79" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D79" t="n">
         <v>14</v>
       </c>
       <c r="E79" t="n">
-        <v>0.9507716298103333</v>
+        <v>0.952945351600647</v>
       </c>
       <c r="F79" t="n">
-        <v>0.04642413556575775</v>
+        <v>0.0609440803527832</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0.9760348796844482</v>
+        <v>0.9710796475410461</v>
       </c>
       <c r="I79" t="n">
-        <v>0.9452669024467468</v>
+        <v>0.8907608389854431</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3442,16 +3454,16 @@
         <v>2014</v>
       </c>
       <c r="C80" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D80" t="n">
         <v>14</v>
       </c>
       <c r="E80" t="n">
-        <v>0.9808302521705627</v>
+        <v>0.979756772518158</v>
       </c>
       <c r="F80" t="n">
-        <v>0.6268249154090881</v>
+        <v>0.5960350036621094</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3459,10 +3471,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>0.9323301911354065</v>
+        <v>0.9603078365325928</v>
       </c>
       <c r="I80" t="n">
-        <v>0.328879177570343</v>
+        <v>0.7281654477119446</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -3480,27 +3492,27 @@
         <v>2015</v>
       </c>
       <c r="C81" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D81" t="n">
         <v>14</v>
       </c>
       <c r="E81" t="n">
-        <v>0.9534465670585632</v>
+        <v>0.9406729936599731</v>
       </c>
       <c r="F81" t="n">
-        <v>0.05916203558444977</v>
+        <v>0.02073950693011284</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>0.9293680787086487</v>
+        <v>0.9388506412506104</v>
       </c>
       <c r="I81" t="n">
-        <v>0.2989737987518311</v>
+        <v>0.4037942588329315</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -3518,16 +3530,16 @@
         <v>2016</v>
       </c>
       <c r="C82" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D82" t="n">
         <v>14</v>
       </c>
       <c r="E82" t="n">
-        <v>0.9639956951141357</v>
+        <v>0.96140056848526</v>
       </c>
       <c r="F82" t="n">
-        <v>0.1548515260219574</v>
+        <v>0.1299634277820587</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3535,10 +3547,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>0.9119969010353088</v>
+        <v>0.9324694871902466</v>
       </c>
       <c r="I82" t="n">
-        <v>0.168463334441185</v>
+        <v>0.3303476870059967</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -3556,16 +3568,16 @@
         <v>2017</v>
       </c>
       <c r="C83" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D83" t="n">
         <v>14</v>
       </c>
       <c r="E83" t="n">
-        <v>0.9732073545455933</v>
+        <v>0.9581449031829834</v>
       </c>
       <c r="F83" t="n">
-        <v>0.3490339815616608</v>
+        <v>0.0970744788646698</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3573,10 +3585,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>0.9290781617164612</v>
+        <v>0.8900665640830994</v>
       </c>
       <c r="I83" t="n">
-        <v>0.296179860830307</v>
+        <v>0.08101127296686172</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -3594,16 +3606,16 @@
         <v>2018</v>
       </c>
       <c r="C84" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D84" t="n">
         <v>14</v>
       </c>
       <c r="E84" t="n">
-        <v>0.9737787246704102</v>
+        <v>0.9699624180793762</v>
       </c>
       <c r="F84" t="n">
-        <v>0.366127073764801</v>
+        <v>0.2761357724666595</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3611,10 +3623,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>0.9183768630027771</v>
+        <v>0.9188565015792847</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2083696275949478</v>
+        <v>0.2117137163877487</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -3632,16 +3644,16 @@
         <v>2019</v>
       </c>
       <c r="C85" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D85" t="n">
         <v>14</v>
       </c>
       <c r="E85" t="n">
-        <v>0.9644476175308228</v>
+        <v>0.9616777896881104</v>
       </c>
       <c r="F85" t="n">
-        <v>0.1613302081823349</v>
+        <v>0.1332271546125412</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3649,10 +3661,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>0.9557943344116211</v>
+        <v>0.9361812472343445</v>
       </c>
       <c r="I85" t="n">
-        <v>0.6536681652069092</v>
+        <v>0.3715855181217194</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -3670,16 +3682,16 @@
         <v>2020</v>
       </c>
       <c r="C86" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D86" t="n">
         <v>14</v>
       </c>
       <c r="E86" t="n">
-        <v>0.9263085126876831</v>
+        <v>0.9267638921737671</v>
       </c>
       <c r="F86" t="n">
-        <v>0.005578257143497467</v>
+        <v>0.006465185433626175</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3687,10 +3699,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>0.8392065763473511</v>
+        <v>0.8427714109420776</v>
       </c>
       <c r="I86" t="n">
-        <v>0.01590072922408581</v>
+        <v>0.01774341613054276</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -3708,16 +3720,16 @@
         <v>2021</v>
       </c>
       <c r="C87" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D87" t="n">
         <v>14</v>
       </c>
       <c r="E87" t="n">
-        <v>0.9713068008422852</v>
+        <v>0.9731912612915039</v>
       </c>
       <c r="F87" t="n">
-        <v>0.2968257963657379</v>
+        <v>0.362033873796463</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3725,10 +3737,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>0.9637293815612793</v>
+        <v>0.9454265236854553</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7836980223655701</v>
+        <v>0.4921994507312775</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -3746,16 +3758,16 @@
         <v>2022</v>
       </c>
       <c r="C88" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D88" t="n">
         <v>14</v>
       </c>
       <c r="E88" t="n">
-        <v>0.9782243967056274</v>
+        <v>0.9792662858963013</v>
       </c>
       <c r="F88" t="n">
-        <v>0.5209853649139404</v>
+        <v>0.5762422680854797</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3763,10 +3775,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>0.9676216244697571</v>
+        <v>0.9673429727554321</v>
       </c>
       <c r="I88" t="n">
-        <v>0.8433278799057007</v>
+        <v>0.8392449021339417</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -3784,16 +3796,16 @@
         <v>2023</v>
       </c>
       <c r="C89" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D89" t="n">
         <v>14</v>
       </c>
       <c r="E89" t="n">
-        <v>0.9761060476303101</v>
+        <v>0.9740513563156128</v>
       </c>
       <c r="F89" t="n">
-        <v>0.4425006806850433</v>
+        <v>0.3882711827754974</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3801,14 +3813,14 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>0.9424606561660767</v>
+        <v>0.8214796781539917</v>
       </c>
       <c r="I89" t="n">
-        <v>0.4507598280906677</v>
+        <v>0.00931656826287508</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -3822,16 +3834,16 @@
         <v>2024</v>
       </c>
       <c r="C90" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D90" t="n">
         <v>14</v>
       </c>
       <c r="E90" t="n">
-        <v>0.9790975451469421</v>
+        <v>0.9793112277984619</v>
       </c>
       <c r="F90" t="n">
-        <v>0.5555065870285034</v>
+        <v>0.5780442357063293</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3839,10 +3851,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>0.9598404765129089</v>
+        <v>0.9608359932899475</v>
       </c>
       <c r="I90" t="n">
-        <v>0.7204660773277283</v>
+        <v>0.7368439435958862</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -3860,16 +3872,16 @@
         <v>2025</v>
       </c>
       <c r="C91" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D91" t="n">
         <v>14</v>
       </c>
       <c r="E91" t="n">
-        <v>0.9708973169326782</v>
+        <v>0.9740586876869202</v>
       </c>
       <c r="F91" t="n">
-        <v>0.2864930629730225</v>
+        <v>0.3885015547275543</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3877,10 +3889,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>0.8833082318305969</v>
+        <v>0.8921041488647461</v>
       </c>
       <c r="I91" t="n">
-        <v>0.06479040533304214</v>
+        <v>0.08668256551027298</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -3898,27 +3910,27 @@
         <v>1996</v>
       </c>
       <c r="C92" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D92" t="n">
         <v>14</v>
       </c>
       <c r="E92" t="n">
-        <v>0.9527694582939148</v>
+        <v>0.9457308650016785</v>
       </c>
       <c r="F92" t="n">
-        <v>0.05563292652368546</v>
+        <v>0.03218483179807663</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>0.8189430236816406</v>
+        <v>0.771867573261261</v>
       </c>
       <c r="I92" t="n">
-        <v>0.008643001317977905</v>
+        <v>0.002287224400788546</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -3936,16 +3948,16 @@
         <v>1997</v>
       </c>
       <c r="C93" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D93" t="n">
         <v>14</v>
       </c>
       <c r="E93" t="n">
-        <v>0.9308242797851562</v>
+        <v>0.9456456899642944</v>
       </c>
       <c r="F93" t="n">
-        <v>0.008121975697577</v>
+        <v>0.03194570541381836</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3953,14 +3965,14 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>0.9204361438751221</v>
+        <v>0.7017583847045898</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2230939865112305</v>
+        <v>0.0003853078815154731</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -3974,16 +3986,16 @@
         <v>1998</v>
       </c>
       <c r="C94" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D94" t="n">
         <v>14</v>
       </c>
       <c r="E94" t="n">
-        <v>0.9539946317672729</v>
+        <v>0.9619665145874023</v>
       </c>
       <c r="F94" t="n">
-        <v>0.06218542531132698</v>
+        <v>0.1367107629776001</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3991,10 +4003,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>0.8183836936950684</v>
+        <v>0.7759679555892944</v>
       </c>
       <c r="I94" t="n">
-        <v>0.008501569740474224</v>
+        <v>0.002556244377046824</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -4012,27 +4024,27 @@
         <v>1999</v>
       </c>
       <c r="C95" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D95" t="n">
         <v>14</v>
       </c>
       <c r="E95" t="n">
-        <v>0.9520867466926575</v>
+        <v>0.9320385456085205</v>
       </c>
       <c r="F95" t="n">
-        <v>0.05229219049215317</v>
+        <v>0.009981125593185425</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>0.9557336568832397</v>
+        <v>0.9629454612731934</v>
       </c>
       <c r="I95" t="n">
-        <v>0.6526721715927124</v>
+        <v>0.7711527347564697</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -4050,16 +4062,16 @@
         <v>2000</v>
       </c>
       <c r="C96" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D96" t="n">
         <v>14</v>
       </c>
       <c r="E96" t="n">
-        <v>0.9039103388786316</v>
+        <v>0.9059115648269653</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0009621345088817179</v>
+        <v>0.001274884911254048</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4067,10 +4079,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>0.847802996635437</v>
+        <v>0.8667072653770447</v>
       </c>
       <c r="I96" t="n">
-        <v>0.02073865011334419</v>
+        <v>0.03773316740989685</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -4088,16 +4100,16 @@
         <v>2001</v>
       </c>
       <c r="C97" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D97" t="n">
         <v>14</v>
       </c>
       <c r="E97" t="n">
-        <v>0.9261599183082581</v>
+        <v>0.9139843583106995</v>
       </c>
       <c r="F97" t="n">
-        <v>0.005510410293936729</v>
+        <v>0.002349285641685128</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4105,14 +4117,14 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>0.8767879009246826</v>
+        <v>0.8669604659080505</v>
       </c>
       <c r="I97" t="n">
-        <v>0.05231615900993347</v>
+        <v>0.03804179653525352</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -4126,27 +4138,27 @@
         <v>2002</v>
       </c>
       <c r="C98" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D98" t="n">
         <v>14</v>
       </c>
       <c r="E98" t="n">
-        <v>0.9458416700363159</v>
+        <v>0.9666123986244202</v>
       </c>
       <c r="F98" t="n">
-        <v>0.02982595004141331</v>
+        <v>0.2064671218395233</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>0.9408548474311829</v>
+        <v>0.93682461977005</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4293881356716156</v>
+        <v>0.3791517615318298</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -4164,16 +4176,16 @@
         <v>2003</v>
       </c>
       <c r="C99" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D99" t="n">
         <v>14</v>
       </c>
       <c r="E99" t="n">
-        <v>0.924748957157135</v>
+        <v>0.9344568252563477</v>
       </c>
       <c r="F99" t="n">
-        <v>0.004907829221338034</v>
+        <v>0.01221910119056702</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4181,10 +4193,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>0.8546484112739563</v>
+        <v>0.8583540320396423</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0256999246776104</v>
+        <v>0.02889519184827805</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -4202,16 +4214,16 @@
         <v>2004</v>
       </c>
       <c r="C100" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D100" t="n">
         <v>14</v>
       </c>
       <c r="E100" t="n">
-        <v>0.9604146480560303</v>
+        <v>0.9611152410507202</v>
       </c>
       <c r="F100" t="n">
-        <v>0.1117406636476517</v>
+        <v>0.1266875267028809</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4219,10 +4231,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>0.8324806690216064</v>
+        <v>0.8556726574897766</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0129545284435153</v>
+        <v>0.02654403448104858</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -4240,27 +4252,27 @@
         <v>2005</v>
       </c>
       <c r="C101" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D101" t="n">
         <v>14</v>
       </c>
       <c r="E101" t="n">
-        <v>0.9684469103813171</v>
+        <v>0.9481124877929688</v>
       </c>
       <c r="F101" t="n">
-        <v>0.2310374826192856</v>
+        <v>0.03968317806720734</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>0.9454530477523804</v>
+        <v>0.9495173692703247</v>
       </c>
       <c r="I101" t="n">
-        <v>0.4925808310508728</v>
+        <v>0.5532371997833252</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -4278,16 +4290,16 @@
         <v>2006</v>
       </c>
       <c r="C102" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D102" t="n">
         <v>14</v>
       </c>
       <c r="E102" t="n">
-        <v>0.9098331332206726</v>
+        <v>0.908159077167511</v>
       </c>
       <c r="F102" t="n">
-        <v>0.001506072585470974</v>
+        <v>0.001508181681856513</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -4295,10 +4307,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>0.7966015934944153</v>
+        <v>0.6668213605880737</v>
       </c>
       <c r="I102" t="n">
-        <v>0.004531917162239552</v>
+        <v>0.0001709944772301242</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -4316,16 +4328,16 @@
         <v>2007</v>
       </c>
       <c r="C103" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D103" t="n">
         <v>14</v>
       </c>
       <c r="E103" t="n">
-        <v>0.9696846604347229</v>
+        <v>0.9580914974212646</v>
       </c>
       <c r="F103" t="n">
-        <v>0.2577154934406281</v>
+        <v>0.09661045670509338</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -4333,10 +4345,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>0.962047815322876</v>
+        <v>0.9642800092697144</v>
       </c>
       <c r="I103" t="n">
-        <v>0.7566363215446472</v>
+        <v>0.792424201965332</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -4354,31 +4366,31 @@
         <v>2008</v>
       </c>
       <c r="C104" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D104" t="n">
         <v>14</v>
       </c>
       <c r="E104" t="n">
-        <v>0.951765239238739</v>
+        <v>0.9364840388298035</v>
       </c>
       <c r="F104" t="n">
-        <v>0.05079083144664764</v>
+        <v>0.01449968665838242</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>0.9449138641357422</v>
+        <v>0.7461294531822205</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4848584532737732</v>
+        <v>0.001159465638920665</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -4392,16 +4404,16 @@
         <v>2009</v>
       </c>
       <c r="C105" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D105" t="n">
         <v>14</v>
       </c>
       <c r="E105" t="n">
-        <v>0.9821816682815552</v>
+        <v>0.9752376079559326</v>
       </c>
       <c r="F105" t="n">
-        <v>0.6839555501937866</v>
+        <v>0.4268011748790741</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -4409,10 +4421,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>0.9190107583999634</v>
+        <v>0.9324973821640015</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2128003984689713</v>
+        <v>0.3306417465209961</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -4430,16 +4442,16 @@
         <v>2010</v>
       </c>
       <c r="C106" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D106" t="n">
         <v>14</v>
       </c>
       <c r="E106" t="n">
-        <v>0.9763928055763245</v>
+        <v>0.9698208570480347</v>
       </c>
       <c r="F106" t="n">
-        <v>0.4526476562023163</v>
+        <v>0.2728095650672913</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -4447,10 +4459,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>0.8856115937232971</v>
+        <v>0.91424161195755</v>
       </c>
       <c r="I106" t="n">
-        <v>0.06990371644496918</v>
+        <v>0.1815728098154068</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -4468,16 +4480,16 @@
         <v>2011</v>
       </c>
       <c r="C107" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D107" t="n">
         <v>14</v>
       </c>
       <c r="E107" t="n">
-        <v>0.9796465039253235</v>
+        <v>0.9717512726783752</v>
       </c>
       <c r="F107" t="n">
-        <v>0.5777474045753479</v>
+        <v>0.3213026225566864</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -4485,14 +4497,14 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>0.8756003379821777</v>
+        <v>0.8718439340591431</v>
       </c>
       <c r="I107" t="n">
-        <v>0.05032782256603241</v>
+        <v>0.04454180598258972</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -4506,16 +4518,16 @@
         <v>2012</v>
       </c>
       <c r="C108" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D108" t="n">
         <v>14</v>
       </c>
       <c r="E108" t="n">
-        <v>0.9564812183380127</v>
+        <v>0.9530296921730042</v>
       </c>
       <c r="F108" t="n">
-        <v>0.07800541818141937</v>
+        <v>0.06140454486012459</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -4523,10 +4535,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>0.947258472442627</v>
+        <v>0.9412697553634644</v>
       </c>
       <c r="I108" t="n">
-        <v>0.5190089344978333</v>
+        <v>0.4348374605178833</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -4544,16 +4556,16 @@
         <v>2013</v>
       </c>
       <c r="C109" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D109" t="n">
         <v>14</v>
       </c>
       <c r="E109" t="n">
-        <v>0.9287801384925842</v>
+        <v>0.9168771505355835</v>
       </c>
       <c r="F109" t="n">
-        <v>0.006845555733889341</v>
+        <v>0.002939922036603093</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -4561,10 +4573,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>0.9589394927024841</v>
+        <v>0.9596476554870605</v>
       </c>
       <c r="I109" t="n">
-        <v>0.7055906057357788</v>
+        <v>0.7172859311103821</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -4582,16 +4594,16 @@
         <v>2014</v>
       </c>
       <c r="C110" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D110" t="n">
         <v>14</v>
       </c>
       <c r="E110" t="n">
-        <v>0.9703262448310852</v>
+        <v>0.9654297828674316</v>
       </c>
       <c r="F110" t="n">
-        <v>0.2726051807403564</v>
+        <v>0.1860328316688538</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -4599,10 +4611,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>0.9148074388504028</v>
+        <v>0.9213986396789551</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1850314289331436</v>
+        <v>0.2303107678890228</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -4620,16 +4632,16 @@
         <v>2015</v>
       </c>
       <c r="C111" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D111" t="n">
         <v>14</v>
       </c>
       <c r="E111" t="n">
-        <v>0.9278033971786499</v>
+        <v>0.9208241105079651</v>
       </c>
       <c r="F111" t="n">
-        <v>0.006311895791441202</v>
+        <v>0.004010655451565981</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -4637,10 +4649,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>0.9399917125701904</v>
+        <v>0.9411482810974121</v>
       </c>
       <c r="I111" t="n">
-        <v>0.4182179570198059</v>
+        <v>0.4332367479801178</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -4658,16 +4670,16 @@
         <v>2016</v>
       </c>
       <c r="C112" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D112" t="n">
         <v>14</v>
       </c>
       <c r="E112" t="n">
-        <v>0.9610417485237122</v>
+        <v>0.9735607504844666</v>
       </c>
       <c r="F112" t="n">
-        <v>0.1183267161250114</v>
+        <v>0.3731295168399811</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -4675,10 +4687,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>0.9422651529312134</v>
+        <v>0.929470956325531</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4481171667575836</v>
+        <v>0.299970805644989</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -4696,16 +4708,16 @@
         <v>2017</v>
       </c>
       <c r="C113" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D113" t="n">
         <v>14</v>
       </c>
       <c r="E113" t="n">
-        <v>0.9365026354789734</v>
+        <v>0.9300095438957214</v>
       </c>
       <c r="F113" t="n">
-        <v>0.0131622301414609</v>
+        <v>0.008435998111963272</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -4713,10 +4725,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>0.8935231566429138</v>
+        <v>0.9128044843673706</v>
       </c>
       <c r="I113" t="n">
-        <v>0.09087181836366653</v>
+        <v>0.1730693131685257</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -4734,27 +4746,27 @@
         <v>2018</v>
       </c>
       <c r="C114" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D114" t="n">
         <v>14</v>
       </c>
       <c r="E114" t="n">
-        <v>0.8749496936798096</v>
+        <v>0.9531915187835693</v>
       </c>
       <c r="F114" t="n">
-        <v>0.0001254038797924295</v>
+        <v>0.06229797750711441</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>0.8380471467971802</v>
+        <v>0.8081453442573547</v>
       </c>
       <c r="I114" t="n">
-        <v>0.01534602139145136</v>
+        <v>0.006304818671196699</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -4772,16 +4784,16 @@
         <v>2019</v>
       </c>
       <c r="C115" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D115" t="n">
         <v>14</v>
       </c>
       <c r="E115" t="n">
-        <v>0.979505181312561</v>
+        <v>0.9784320592880249</v>
       </c>
       <c r="F115" t="n">
-        <v>0.5719851851463318</v>
+        <v>0.5432323217391968</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -4789,10 +4801,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>0.9671123623847961</v>
+        <v>0.8888908624649048</v>
       </c>
       <c r="I115" t="n">
-        <v>0.8358405232429504</v>
+        <v>0.07791390269994736</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -4810,16 +4822,16 @@
         <v>2020</v>
       </c>
       <c r="C116" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D116" t="n">
         <v>14</v>
       </c>
       <c r="E116" t="n">
-        <v>0.9528724551200867</v>
+        <v>0.971264123916626</v>
       </c>
       <c r="F116" t="n">
-        <v>0.05615552514791489</v>
+        <v>0.3084166646003723</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -4827,10 +4839,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>0.916663646697998</v>
+        <v>0.9128100275993347</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1968336850404739</v>
+        <v>0.1731012761592865</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -4848,16 +4860,16 @@
         <v>2021</v>
       </c>
       <c r="C117" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D117" t="n">
         <v>14</v>
       </c>
       <c r="E117" t="n">
-        <v>0.9791237115859985</v>
+        <v>0.9778451919555664</v>
       </c>
       <c r="F117" t="n">
-        <v>0.556556761264801</v>
+        <v>0.5205783843994141</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -4865,10 +4877,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>0.9108024835586548</v>
+        <v>0.9119818806648254</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1618713289499283</v>
+        <v>0.1683787852525711</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -4886,16 +4898,16 @@
         <v>2022</v>
       </c>
       <c r="C118" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D118" t="n">
         <v>14</v>
       </c>
       <c r="E118" t="n">
-        <v>0.9655568599700928</v>
+        <v>0.9614232778549194</v>
       </c>
       <c r="F118" t="n">
-        <v>0.1783545613288879</v>
+        <v>0.1302278190851212</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -4903,10 +4915,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>0.9119310975074768</v>
+        <v>0.9137703776359558</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1680931448936462</v>
+        <v>0.1787403523921967</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -4924,16 +4936,16 @@
         <v>2023</v>
       </c>
       <c r="C119" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D119" t="n">
         <v>14</v>
       </c>
       <c r="E119" t="n">
-        <v>0.961820125579834</v>
+        <v>0.9650686979293823</v>
       </c>
       <c r="F119" t="n">
-        <v>0.1270372271537781</v>
+        <v>0.1801852881908417</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -4941,10 +4953,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>0.9101036190986633</v>
+        <v>0.9139745831489563</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1581328809261322</v>
+        <v>0.1799622178077698</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -4962,16 +4974,16 @@
         <v>2024</v>
       </c>
       <c r="C120" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D120" t="n">
         <v>14</v>
       </c>
       <c r="E120" t="n">
-        <v>0.8617748618125916</v>
+        <v>0.8272483348846436</v>
       </c>
       <c r="F120" t="n">
-        <v>5.347151454770938e-05</v>
+        <v>8.280952897621319e-06</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -4979,10 +4991,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>0.9039544463157654</v>
+        <v>0.9118813276290894</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1287287920713425</v>
+        <v>0.1678139567375183</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -5000,16 +5012,16 @@
         <v>2025</v>
       </c>
       <c r="C121" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D121" t="n">
         <v>14</v>
       </c>
       <c r="E121" t="n">
-        <v>0.9827061891555786</v>
+        <v>0.9793687462806702</v>
       </c>
       <c r="F121" t="n">
-        <v>0.7061882615089417</v>
+        <v>0.5803555846214294</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -5017,10 +5029,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>0.841742992401123</v>
+        <v>0.8427853584289551</v>
       </c>
       <c r="I121" t="n">
-        <v>0.01718964986503124</v>
+        <v>0.01775103807449341</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
